--- a/data/vendor-search/results_all_shades.xlsx
+++ b/data/vendor-search/results_all_shades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>cpe_strings</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>matched_terms</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,6 +492,11 @@
           <t>cpe:2.3:a:rtl_433_project:rlt_433:21.12:*:*:*:*:*:*:*</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>somfy</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +528,11 @@
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>powerview</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -549,6 +564,11 @@
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>powerview</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -580,6 +600,11 @@
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>powerview</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -611,6 +636,11 @@
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>powerview</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
